--- a/powerbi/Kristiansand_EPM_PowerBI_Model.xlsx
+++ b/powerbi/Kristiansand_EPM_PowerBI_Model.xlsx
@@ -47625,7 +47625,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="77" customWidth="1" min="2" max="2"/>
+    <col width="68" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -47646,7 +47646,7 @@
     <row r="3">
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Konsolidert avviksoppfølging: Mevold Grunnskole vs. Slettheia Bofellesskap</t>
+          <t>Konsolidert avviksoppfølging: Kommunal Skole vs. Kommunal Boenhet</t>
         </is>
       </c>
     </row>
